--- a/docs/국가유산450_반영_점검.xlsx
+++ b/docs/국가유산450_반영_점검.xlsx
@@ -43789,16 +43789,16 @@
         <v>0</v>
       </c>
       <c r="C8" s="2">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="D8" s="2">
-        <v>18500</v>
+        <v>19000</v>
       </c>
       <c r="E8" s="2">
-        <v>46500</v>
+        <v>47500</v>
       </c>
       <c r="F8" s="2">
-        <v>88000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="9">

--- a/docs/국가유산450_반영_점검.xlsx
+++ b/docs/국가유산450_반영_점검.xlsx
@@ -43798,7 +43798,7 @@
         <v>47500</v>
       </c>
       <c r="F8" s="2">
-        <v>90000</v>
+        <v>90500</v>
       </c>
     </row>
     <row r="9">
